--- a/artfynd/A 51549-2022 artfynd.xlsx
+++ b/artfynd/A 51549-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120130268</v>
+        <v>120130267</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 fk i stig, ytterkant av contorta</t>
+          <t>2 fk i stig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120130267</v>
+        <v>120130268</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 fk i stig</t>
+          <t>3 fk i stig, ytterkant av contorta</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 51549-2022 artfynd.xlsx
+++ b/artfynd/A 51549-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120130267</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>120130268</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 51549-2022 artfynd.xlsx
+++ b/artfynd/A 51549-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120130267</v>
+        <v>120130268</v>
       </c>
       <c r="B2" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 fk i stig</t>
+          <t>3 fk i stig, ytterkant av contorta</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120130268</v>
+        <v>120130267</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>3 fk i stig, ytterkant av contorta</t>
+          <t>2 fk i stig</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 51549-2022 artfynd.xlsx
+++ b/artfynd/A 51549-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120130268</v>
+        <v>120130267</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>3 fk i stig, ytterkant av contorta</t>
+          <t>2 fk i stig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120130267</v>
+        <v>120130268</v>
       </c>
       <c r="B3" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 fk i stig</t>
+          <t>3 fk i stig, ytterkant av contorta</t>
         </is>
       </c>
       <c r="AD3" t="b">
